--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/44.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/44.xlsx
@@ -426,13 +426,13 @@
         <v>-7.042373312489702</v>
       </c>
       <c r="E2">
-        <v>-14.93868157285283</v>
+        <v>-13.71127944933985</v>
       </c>
       <c r="F2">
-        <v>-3.607405162552698</v>
+        <v>-4.029354808353697</v>
       </c>
       <c r="G2">
-        <v>-9.96336934747581</v>
+        <v>-8.515376455145063</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.03336725855767</v>
       </c>
       <c r="E3">
-        <v>-14.48698440448374</v>
+        <v>-12.66987986721792</v>
       </c>
       <c r="F3">
-        <v>-3.756465734849455</v>
+        <v>-3.775060097940096</v>
       </c>
       <c r="G3">
-        <v>-7.868674626230594</v>
+        <v>-8.200301904536007</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.938612665558158</v>
       </c>
       <c r="E4">
-        <v>-14.05726844894789</v>
+        <v>-14.36757760184949</v>
       </c>
       <c r="F4">
-        <v>-3.841195294644803</v>
+        <v>-4.124505230076262</v>
       </c>
       <c r="G4">
-        <v>-8.840140972547568</v>
+        <v>-8.045914613312094</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.757750549368413</v>
       </c>
       <c r="E5">
-        <v>-15.18092776141915</v>
+        <v>-14.68186728340384</v>
       </c>
       <c r="F5">
-        <v>-4.068416473232707</v>
+        <v>-3.925903316887677</v>
       </c>
       <c r="G5">
-        <v>-7.979101183238524</v>
+        <v>-7.391840199481669</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.498666949511526</v>
       </c>
       <c r="E6">
-        <v>-15.27820844005192</v>
+        <v>-14.66518438515958</v>
       </c>
       <c r="F6">
-        <v>-4.140325390734927</v>
+        <v>-3.771758225472537</v>
       </c>
       <c r="G6">
-        <v>-8.559823839555319</v>
+        <v>-7.772480104495991</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.168655730771673</v>
       </c>
       <c r="E7">
-        <v>-16.11685465542843</v>
+        <v>-15.79943126986077</v>
       </c>
       <c r="F7">
-        <v>-3.56303283425434</v>
+        <v>-4.081047419390594</v>
       </c>
       <c r="G7">
-        <v>-8.176456045016636</v>
+        <v>-8.187205386382649</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.775360646616076</v>
       </c>
       <c r="E8">
-        <v>-18.19831791984002</v>
+        <v>-16.96343475726637</v>
       </c>
       <c r="F8">
-        <v>-4.280595328153176</v>
+        <v>-4.093445594308294</v>
       </c>
       <c r="G8">
-        <v>-7.965326003249617</v>
+        <v>-8.130949286033815</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.333458707514978</v>
       </c>
       <c r="E9">
-        <v>-17.09424425745194</v>
+        <v>-16.81908059132386</v>
       </c>
       <c r="F9">
-        <v>-3.798222907257176</v>
+        <v>-3.815047049208034</v>
       </c>
       <c r="G9">
-        <v>-7.482744469444516</v>
+        <v>-7.309510242465533</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.85469070441115</v>
       </c>
       <c r="E10">
-        <v>-19.07957707562871</v>
+        <v>-16.83177843244137</v>
       </c>
       <c r="F10">
-        <v>-3.809484562098235</v>
+        <v>-3.696610391425371</v>
       </c>
       <c r="G10">
-        <v>-7.294390980987682</v>
+        <v>-7.385993776059316</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.349875357645011</v>
       </c>
       <c r="E11">
-        <v>-18.26766697079348</v>
+        <v>-18.77929396418008</v>
       </c>
       <c r="F11">
-        <v>-3.854039959592612</v>
+        <v>-3.668213128490001</v>
       </c>
       <c r="G11">
-        <v>-7.362300201634752</v>
+        <v>-6.479808077231231</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.830429826603262</v>
       </c>
       <c r="E12">
-        <v>-18.87697767699954</v>
+        <v>-18.91140766487986</v>
       </c>
       <c r="F12">
-        <v>-3.65733252265423</v>
+        <v>-3.411341367086292</v>
       </c>
       <c r="G12">
-        <v>-6.284995714427279</v>
+        <v>-6.867681524248861</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.306294681279116</v>
       </c>
       <c r="E13">
-        <v>-19.52725295907898</v>
+        <v>-19.28249346743841</v>
       </c>
       <c r="F13">
-        <v>-3.886726508939678</v>
+        <v>-3.467809516200329</v>
       </c>
       <c r="G13">
-        <v>-6.086296771160223</v>
+        <v>-6.348637641874229</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.796249722581702</v>
       </c>
       <c r="E14">
-        <v>-18.63436015356459</v>
+        <v>-20.50294438334961</v>
       </c>
       <c r="F14">
-        <v>-2.82859980983009</v>
+        <v>-3.271333193767328</v>
       </c>
       <c r="G14">
-        <v>-7.25283701337875</v>
+        <v>-5.522683014190382</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.314796537515245</v>
       </c>
       <c r="E15">
-        <v>-22.06694345137872</v>
+        <v>-21.36273857234194</v>
       </c>
       <c r="F15">
-        <v>-2.318925227705221</v>
+        <v>-2.870389288566519</v>
       </c>
       <c r="G15">
-        <v>-6.070174414383972</v>
+        <v>-5.010915710911067</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.87673833437139</v>
       </c>
       <c r="E16">
-        <v>-22.68018940149744</v>
+        <v>-21.6674731737401</v>
       </c>
       <c r="F16">
-        <v>-3.016982154370337</v>
+        <v>-2.84414329577622</v>
       </c>
       <c r="G16">
-        <v>-5.75194491387599</v>
+        <v>-5.414385137964203</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.494570391220624</v>
       </c>
       <c r="E17">
-        <v>-23.17844381113939</v>
+        <v>-23.48112701381208</v>
       </c>
       <c r="F17">
-        <v>-2.428386524678551</v>
+        <v>-2.722791613103106</v>
       </c>
       <c r="G17">
-        <v>-4.939563522903154</v>
+        <v>-4.56529310750639</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.177287526554798</v>
       </c>
       <c r="E18">
-        <v>-23.79928401216898</v>
+        <v>-23.06055404729771</v>
       </c>
       <c r="F18">
-        <v>-1.729110241196515</v>
+        <v>-2.472937780335914</v>
       </c>
       <c r="G18">
-        <v>-4.655697485092808</v>
+        <v>-3.987116260709295</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.9313941263692364</v>
       </c>
       <c r="E19">
-        <v>-25.42006108730626</v>
+        <v>-25.05892434214256</v>
       </c>
       <c r="F19">
-        <v>-1.96667938538019</v>
+        <v>-2.241728841070933</v>
       </c>
       <c r="G19">
-        <v>-3.72508658127598</v>
+        <v>-3.762297113137389</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.7527559765239724</v>
       </c>
       <c r="E20">
-        <v>-25.07566611054892</v>
+        <v>-25.4117603944502</v>
       </c>
       <c r="F20">
-        <v>-1.865944110627951</v>
+        <v>-2.339293953772658</v>
       </c>
       <c r="G20">
-        <v>-3.985484161758434</v>
+        <v>-4.141960407217626</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6302291703697229</v>
       </c>
       <c r="E21">
-        <v>-26.57279320290676</v>
+        <v>-24.99653102726488</v>
       </c>
       <c r="F21">
-        <v>-1.743323369093748</v>
+        <v>-1.567980355840969</v>
       </c>
       <c r="G21">
-        <v>-3.977449467734623</v>
+        <v>-3.495930619047629</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5477356522037394</v>
       </c>
       <c r="E22">
-        <v>-25.59243745040823</v>
+        <v>-26.79977843406723</v>
       </c>
       <c r="F22">
-        <v>-1.658384232345493</v>
+        <v>-1.254288389177032</v>
       </c>
       <c r="G22">
-        <v>-3.262103477063366</v>
+        <v>-3.65931266250174</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.4866024387774325</v>
       </c>
       <c r="E23">
-        <v>-29.0869748011213</v>
+        <v>-28.05351816240882</v>
       </c>
       <c r="F23">
-        <v>-0.9878763203952806</v>
+        <v>-1.389870595462839</v>
       </c>
       <c r="G23">
-        <v>-3.581786307063088</v>
+        <v>-3.455790254383966</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.4281595368683829</v>
       </c>
       <c r="E24">
-        <v>-28.22627944580145</v>
+        <v>-28.18116678773703</v>
       </c>
       <c r="F24">
-        <v>-1.113803076234056</v>
+        <v>-1.4435645421449</v>
       </c>
       <c r="G24">
-        <v>-3.564247036796029</v>
+        <v>-2.800706124164062</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.352878743369831</v>
       </c>
       <c r="E25">
-        <v>-27.77657480599573</v>
+        <v>-27.92805226155231</v>
       </c>
       <c r="F25">
-        <v>-0.5533238929280907</v>
+        <v>-1.091153026339309</v>
       </c>
       <c r="G25">
-        <v>-4.723000875906191</v>
+        <v>-2.939007474612655</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.2441520015052232</v>
       </c>
       <c r="E26">
-        <v>-29.52119205982078</v>
+        <v>-28.60007327581658</v>
       </c>
       <c r="F26">
-        <v>-0.6905305276907868</v>
+        <v>-0.9678960986397565</v>
       </c>
       <c r="G26">
-        <v>-3.939421231125015</v>
+        <v>-3.218688982861363</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.08972542238791531</v>
       </c>
       <c r="E27">
-        <v>-29.6391067302695</v>
+        <v>-28.88001901049675</v>
       </c>
       <c r="F27">
-        <v>-0.6370436728594255</v>
+        <v>-1.03356575286409</v>
       </c>
       <c r="G27">
-        <v>-3.120789530174036</v>
+        <v>-2.764326539233011</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.1199561528493436</v>
       </c>
       <c r="E28">
-        <v>-29.81477302973805</v>
+        <v>-28.91350254730947</v>
       </c>
       <c r="F28">
-        <v>-0.777798205208312</v>
+        <v>-0.6927646345761371</v>
       </c>
       <c r="G28">
-        <v>-4.695894129030639</v>
+        <v>-3.290302703966878</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.389409901969084</v>
       </c>
       <c r="E29">
-        <v>-30.12237868365707</v>
+        <v>-29.54540128186578</v>
       </c>
       <c r="F29">
-        <v>-0.5146233962367006</v>
+        <v>-0.9143322056399349</v>
       </c>
       <c r="G29">
-        <v>-4.602702272100155</v>
+        <v>-3.694017111389921</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.7191422426926871</v>
       </c>
       <c r="E30">
-        <v>-29.23177275751656</v>
+        <v>-28.58241222718667</v>
       </c>
       <c r="F30">
-        <v>-0.3491354699750266</v>
+        <v>-0.8945599041025135</v>
       </c>
       <c r="G30">
-        <v>-4.601652829164205</v>
+        <v>-3.061054046463426</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.103346710272551</v>
       </c>
       <c r="E31">
-        <v>-28.45655687756549</v>
+        <v>-28.55093933283336</v>
       </c>
       <c r="F31">
-        <v>-1.03409839310409</v>
+        <v>-0.8566728642006725</v>
       </c>
       <c r="G31">
-        <v>-5.121580627197824</v>
+        <v>-3.591969545141886</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.53299260024263</v>
       </c>
       <c r="E32">
-        <v>-29.14491209757543</v>
+        <v>-27.79833412360259</v>
       </c>
       <c r="F32">
-        <v>-1.031230585155598</v>
+        <v>-0.9993400968826229</v>
       </c>
       <c r="G32">
-        <v>-3.70351175599655</v>
+        <v>-3.039244172450708</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.99761045634335</v>
       </c>
       <c r="E33">
-        <v>-28.63248356428948</v>
+        <v>-28.03277775145369</v>
       </c>
       <c r="F33">
-        <v>-0.9052599258444747</v>
+        <v>-1.000489870837709</v>
       </c>
       <c r="G33">
-        <v>-4.347058635012094</v>
+        <v>-3.674474961071603</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.483627911338556</v>
       </c>
       <c r="E34">
-        <v>-27.75729709214508</v>
+        <v>-27.62827181071854</v>
       </c>
       <c r="F34">
-        <v>-0.3753508131714225</v>
+        <v>-1.01049157885911</v>
       </c>
       <c r="G34">
-        <v>-3.450360959699561</v>
+        <v>-3.642074651878755</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.976351061767912</v>
       </c>
       <c r="E35">
-        <v>-27.52349650760307</v>
+        <v>-26.6993957507392</v>
       </c>
       <c r="F35">
-        <v>-1.125451578652223</v>
+        <v>-1.010561161720945</v>
       </c>
       <c r="G35">
-        <v>-3.981739934753519</v>
+        <v>-3.678537000448288</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.45815703894042</v>
       </c>
       <c r="E36">
-        <v>-25.97905591881308</v>
+        <v>-25.9830228620438</v>
       </c>
       <c r="F36">
-        <v>-0.8058044787295604</v>
+        <v>-1.086922554013212</v>
       </c>
       <c r="G36">
-        <v>-4.812779560385686</v>
+        <v>-3.790459924039969</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.915596275255621</v>
       </c>
       <c r="E37">
-        <v>-27.21283866220287</v>
+        <v>-25.44851348949645</v>
       </c>
       <c r="F37">
-        <v>-0.6146371629811017</v>
+        <v>-1.254719140226488</v>
       </c>
       <c r="G37">
-        <v>-4.198262855204011</v>
+        <v>-3.33462759819218</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.337817402665963</v>
       </c>
       <c r="E38">
-        <v>-25.54367937076764</v>
+        <v>-25.30073126873014</v>
       </c>
       <c r="F38">
-        <v>-1.01831799408076</v>
+        <v>-1.582403889058514</v>
       </c>
       <c r="G38">
-        <v>-4.262623171032982</v>
+        <v>-3.932935872413583</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.715880261544588</v>
       </c>
       <c r="E39">
-        <v>-25.84899814531279</v>
+        <v>-25.32250870023302</v>
       </c>
       <c r="F39">
-        <v>-0.9078170960169167</v>
+        <v>-1.221682191468038</v>
       </c>
       <c r="G39">
-        <v>-4.335640563447147</v>
+        <v>-3.148776882163034</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.043203149933803</v>
       </c>
       <c r="E40">
-        <v>-26.36530305234931</v>
+        <v>-25.07468796016326</v>
       </c>
       <c r="F40">
-        <v>-0.8942177883651573</v>
+        <v>-1.532535343042581</v>
       </c>
       <c r="G40">
-        <v>-3.789129084733182</v>
+        <v>-3.898330739891581</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.312108621131246</v>
       </c>
       <c r="E41">
-        <v>-24.01717606752204</v>
+        <v>-24.13680476538267</v>
       </c>
       <c r="F41">
-        <v>-1.141611369946035</v>
+        <v>-1.416429711131396</v>
       </c>
       <c r="G41">
-        <v>-4.296629094812376</v>
+        <v>-3.475630353800818</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.52179375088624</v>
       </c>
       <c r="E42">
-        <v>-22.92932339902943</v>
+        <v>-24.37638821123248</v>
       </c>
       <c r="F42">
-        <v>-0.9091764469249107</v>
+        <v>-1.398869978926852</v>
       </c>
       <c r="G42">
-        <v>-4.045653326934688</v>
+        <v>-4.006688205937466</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.673250074400852</v>
       </c>
       <c r="E43">
-        <v>-23.97492540503048</v>
+        <v>-23.60043419001816</v>
       </c>
       <c r="F43">
-        <v>-1.567446887233566</v>
+        <v>-1.780185718518327</v>
       </c>
       <c r="G43">
-        <v>-4.229186661086343</v>
+        <v>-3.45249957211793</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.768496453716685</v>
       </c>
       <c r="E44">
-        <v>-21.56867545631475</v>
+        <v>-21.47784785314291</v>
       </c>
       <c r="F44">
-        <v>-1.460591634109444</v>
+        <v>-1.408276919153044</v>
       </c>
       <c r="G44">
-        <v>-5.204112527491855</v>
+        <v>-3.069429726677783</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.810385023173362</v>
       </c>
       <c r="E45">
-        <v>-23.55742727236732</v>
+        <v>-21.93732493985718</v>
       </c>
       <c r="F45">
-        <v>-0.8292431343917724</v>
+        <v>-1.436891214347947</v>
       </c>
       <c r="G45">
-        <v>-3.745307393429849</v>
+        <v>-3.652608807784716</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.799892448234417</v>
       </c>
       <c r="E46">
-        <v>-21.39963657855644</v>
+        <v>-21.10827456090292</v>
       </c>
       <c r="F46">
-        <v>-0.8498355196579653</v>
+        <v>-1.693263470207769</v>
       </c>
       <c r="G46">
-        <v>-4.045570563296207</v>
+        <v>-2.627399065183215</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.744014630395425</v>
       </c>
       <c r="E47">
-        <v>-21.35532998886539</v>
+        <v>-21.05295925089923</v>
       </c>
       <c r="F47">
-        <v>-0.8291362749968113</v>
+        <v>-1.187137614036493</v>
       </c>
       <c r="G47">
-        <v>-4.258064549825406</v>
+        <v>-3.258640646429288</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.650351368397767</v>
       </c>
       <c r="E48">
-        <v>-19.36262481500413</v>
+        <v>-19.98342425976765</v>
       </c>
       <c r="F48">
-        <v>-1.218398543083341</v>
+        <v>-1.350239842178105</v>
       </c>
       <c r="G48">
-        <v>-4.12317968237334</v>
+        <v>-2.931310456233849</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.525003279368937</v>
       </c>
       <c r="E49">
-        <v>-20.65317198008007</v>
+        <v>-19.31386673536355</v>
       </c>
       <c r="F49">
-        <v>-1.213909620127571</v>
+        <v>-1.391141311058733</v>
       </c>
       <c r="G49">
-        <v>-3.92209383577247</v>
+        <v>-3.091180010870794</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.372590840916072</v>
       </c>
       <c r="E50">
-        <v>-18.70401261227657</v>
+        <v>-19.53506457674221</v>
       </c>
       <c r="F50">
-        <v>-1.217686975484336</v>
+        <v>-1.424781311286421</v>
       </c>
       <c r="G50">
-        <v>-4.341652514146464</v>
+        <v>-3.297023111411598</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.195233048199579</v>
       </c>
       <c r="E51">
-        <v>-18.71550135083403</v>
+        <v>-17.8534610387339</v>
       </c>
       <c r="F51">
-        <v>-1.167105205134593</v>
+        <v>-1.578532928185232</v>
       </c>
       <c r="G51">
-        <v>-2.850784746536617</v>
+        <v>-3.353355354307836</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.998706305072558</v>
       </c>
       <c r="E52">
-        <v>-18.94461949325211</v>
+        <v>-18.06175272919071</v>
       </c>
       <c r="F52">
-        <v>-1.001233744765423</v>
+        <v>-1.514280610587088</v>
       </c>
       <c r="G52">
-        <v>-3.690690013122953</v>
+        <v>-3.057667358376752</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.7872195699566</v>
       </c>
       <c r="E53">
-        <v>-18.14005004478333</v>
+        <v>-17.384750393518</v>
       </c>
       <c r="F53">
-        <v>-1.337464760092131</v>
+        <v>-1.69755441335427</v>
       </c>
       <c r="G53">
-        <v>-3.695486993609357</v>
+        <v>-3.796064677637955</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.562265398471473</v>
       </c>
       <c r="E54">
-        <v>-16.6407447564278</v>
+        <v>-16.0234367651242</v>
       </c>
       <c r="F54">
-        <v>-1.437681476850218</v>
+        <v>-1.475848504934205</v>
       </c>
       <c r="G54">
-        <v>-4.777535492574605</v>
+        <v>-3.759363969789594</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.324015298064956</v>
       </c>
       <c r="E55">
-        <v>-16.30639393501947</v>
+        <v>-16.09053969296986</v>
       </c>
       <c r="F55">
-        <v>-0.9344764441412132</v>
+        <v>-1.618888502947415</v>
       </c>
       <c r="G55">
-        <v>-4.519984981255925</v>
+        <v>-3.926463755884308</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.07120331557477</v>
       </c>
       <c r="E56">
-        <v>-17.56266960880536</v>
+        <v>-15.49903947503597</v>
       </c>
       <c r="F56">
-        <v>-1.374736323013692</v>
+        <v>-1.146608910487125</v>
       </c>
       <c r="G56">
-        <v>-3.779502018304981</v>
+        <v>-3.687799906867169</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.808152716917197</v>
       </c>
       <c r="E57">
-        <v>-14.6223948342611</v>
+        <v>-16.18931929649917</v>
       </c>
       <c r="F57">
-        <v>-1.773416300102649</v>
+        <v>-1.517169956088053</v>
       </c>
       <c r="G57">
-        <v>-4.621857088590377</v>
+        <v>-3.901505553063742</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.53769434073519</v>
       </c>
       <c r="E58">
-        <v>-15.96967472170513</v>
+        <v>-14.63262012857042</v>
       </c>
       <c r="F58">
-        <v>-1.214473738328877</v>
+        <v>-1.417390617318644</v>
       </c>
       <c r="G58">
-        <v>-5.219331105335884</v>
+        <v>-3.91087108639434</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.261969167324145</v>
       </c>
       <c r="E59">
-        <v>-14.42347708500017</v>
+        <v>-14.56240613908149</v>
       </c>
       <c r="F59">
-        <v>-0.9961227178901496</v>
+        <v>-1.442352640634604</v>
       </c>
       <c r="G59">
-        <v>-3.804331109849515</v>
+        <v>-3.808995668514348</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.98339346879249</v>
       </c>
       <c r="E60">
-        <v>-12.48500491585478</v>
+        <v>-12.96103810354109</v>
       </c>
       <c r="F60">
-        <v>-1.542107128381929</v>
+        <v>-1.540280578258756</v>
       </c>
       <c r="G60">
-        <v>-4.123676264204232</v>
+        <v>-3.934750051369103</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>2.703781316347076</v>
       </c>
       <c r="E61">
-        <v>-14.40831575402249</v>
+        <v>-13.56192131961886</v>
       </c>
       <c r="F61">
-        <v>-1.236324413679922</v>
+        <v>-1.433316809004867</v>
       </c>
       <c r="G61">
-        <v>-4.017546795306275</v>
+        <v>-4.055144660995778</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>2.430975054157553</v>
       </c>
       <c r="E62">
-        <v>-15.28417696879403</v>
+        <v>-12.88102449629956</v>
       </c>
       <c r="F62">
-        <v>-1.209140708989654</v>
+        <v>-1.440152496812769</v>
       </c>
       <c r="G62">
-        <v>-4.734150793282456</v>
+        <v>-5.041574673150257</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.169616154582978</v>
       </c>
       <c r="E63">
-        <v>-14.18402496489659</v>
+        <v>-13.08889051019964</v>
       </c>
       <c r="F63">
-        <v>-1.377616556473226</v>
+        <v>-1.588133706383678</v>
       </c>
       <c r="G63">
-        <v>-4.198878616674316</v>
+        <v>-4.016686053466065</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.923833341090083</v>
       </c>
       <c r="E64">
-        <v>-13.27047326095921</v>
+        <v>-11.92413076763476</v>
       </c>
       <c r="F64">
-        <v>-1.691844476846773</v>
+        <v>-1.411610269581909</v>
       </c>
       <c r="G64">
-        <v>-4.963346482057279</v>
+        <v>-4.829458088812534</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.696398648366067</v>
       </c>
       <c r="E65">
-        <v>-13.2489177246827</v>
+        <v>-12.68918475191262</v>
       </c>
       <c r="F65">
-        <v>-1.421586298213823</v>
+        <v>-1.62251178196726</v>
       </c>
       <c r="G65">
-        <v>-4.737189874087507</v>
+        <v>-5.026455411672406</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.489235839519764</v>
       </c>
       <c r="E66">
-        <v>-13.26324128796896</v>
+        <v>-12.32882690427824</v>
       </c>
       <c r="F66">
-        <v>-1.723016770581521</v>
+        <v>-1.494314471077411</v>
       </c>
       <c r="G66">
-        <v>-4.76633591701525</v>
+        <v>-4.816811804852518</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.306661823441935</v>
       </c>
       <c r="E67">
-        <v>-12.38209987250448</v>
+        <v>-13.28373716132768</v>
       </c>
       <c r="F67">
-        <v>-1.543757236248306</v>
+        <v>-1.752836340347498</v>
       </c>
       <c r="G67">
-        <v>-5.077464297341496</v>
+        <v>-4.746863288153257</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.149179585920566</v>
       </c>
       <c r="E68">
-        <v>-12.77801982652109</v>
+        <v>-11.61387595642125</v>
       </c>
       <c r="F68">
-        <v>-1.817526864301723</v>
+        <v>-1.772236704921063</v>
       </c>
       <c r="G68">
-        <v>-5.257074635029115</v>
+        <v>-5.018394233284281</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.016598759489407</v>
       </c>
       <c r="E69">
-        <v>-13.08959242367083</v>
+        <v>-12.26923671481131</v>
       </c>
       <c r="F69">
-        <v>-1.132127391551384</v>
+        <v>-1.556798224270578</v>
       </c>
       <c r="G69">
-        <v>-6.209081594666252</v>
+        <v>-5.070978938630064</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.9073179524774836</v>
       </c>
       <c r="E70">
-        <v>-13.68440748457833</v>
+        <v>-11.59857877122334</v>
       </c>
       <c r="F70">
-        <v>-1.675434518597315</v>
+        <v>-1.606496126601535</v>
       </c>
       <c r="G70">
-        <v>-5.250950125781463</v>
+        <v>-5.003404083082461</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.8218974751703604</v>
       </c>
       <c r="E71">
-        <v>-11.51870554667605</v>
+        <v>-11.90361678038002</v>
       </c>
       <c r="F71">
-        <v>-1.188315552483274</v>
+        <v>-1.829781731658739</v>
       </c>
       <c r="G71">
-        <v>-5.419139081358597</v>
+        <v>-4.792174724949263</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.7625164112398892</v>
       </c>
       <c r="E72">
-        <v>-13.08214761240222</v>
+        <v>-12.20498672559048</v>
       </c>
       <c r="F72">
-        <v>-1.441304755870063</v>
+        <v>-1.667368705196256</v>
       </c>
       <c r="G72">
-        <v>-5.707944453113536</v>
+        <v>-4.873034799745961</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.7306339393643739</v>
       </c>
       <c r="E73">
-        <v>-12.91561298077014</v>
+        <v>-12.90450916250334</v>
       </c>
       <c r="F73">
-        <v>-1.648915164564092</v>
+        <v>-2.065700767976038</v>
       </c>
       <c r="G73">
-        <v>-4.912761346217215</v>
+        <v>-4.64987423548923</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.7280667564769717</v>
       </c>
       <c r="E74">
-        <v>-14.26800551536883</v>
+        <v>-11.89560138138644</v>
       </c>
       <c r="F74">
-        <v>-1.833236852095815</v>
+        <v>-1.725037987044352</v>
       </c>
       <c r="G74">
-        <v>-6.361806992029449</v>
+        <v>-4.858352530279293</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.7557754581161786</v>
       </c>
       <c r="E75">
-        <v>-14.29606394032036</v>
+        <v>-11.39598842954219</v>
       </c>
       <c r="F75">
-        <v>-1.987959315590707</v>
+        <v>-1.897054276807489</v>
       </c>
       <c r="G75">
-        <v>-5.497059391716423</v>
+        <v>-4.321968010369957</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.8179016159296595</v>
       </c>
       <c r="E76">
-        <v>-13.88194857774093</v>
+        <v>-12.83244302714527</v>
       </c>
       <c r="F76">
-        <v>-1.386017030305015</v>
+        <v>-1.976434239915557</v>
       </c>
       <c r="G76">
-        <v>-5.143592444488438</v>
+        <v>-4.973274808129553</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.9179833409314153</v>
       </c>
       <c r="E77">
-        <v>-14.9873083267472</v>
+        <v>-13.22930037528147</v>
       </c>
       <c r="F77">
-        <v>-1.823974876165114</v>
+        <v>-2.244002709591617</v>
       </c>
       <c r="G77">
-        <v>-5.132846413667964</v>
+        <v>-4.585652962572908</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.058610961624076</v>
       </c>
       <c r="E78">
-        <v>-14.25986331910304</v>
+        <v>-14.06370793898679</v>
       </c>
       <c r="F78">
-        <v>-2.206365008278019</v>
+        <v>-2.013611368953199</v>
       </c>
       <c r="G78">
-        <v>-4.630053999345613</v>
+        <v>-4.179922432916449</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.240337199949016</v>
       </c>
       <c r="E79">
-        <v>-14.83706714459471</v>
+        <v>-13.92123308975747</v>
       </c>
       <c r="F79">
-        <v>-2.019302253010432</v>
+        <v>-2.266832515212772</v>
       </c>
       <c r="G79">
-        <v>-5.342927012499034</v>
+        <v>-4.038992509309675</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.461884240272789</v>
       </c>
       <c r="E80">
-        <v>-16.01119629988146</v>
+        <v>-14.17686544749046</v>
       </c>
       <c r="F80">
-        <v>-1.588991066645575</v>
+        <v>-2.364969201422429</v>
       </c>
       <c r="G80">
-        <v>-5.070124817880932</v>
+        <v>-3.439945983433014</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.723146834302748</v>
       </c>
       <c r="E81">
-        <v>-16.77038591031938</v>
+        <v>-15.47869304131951</v>
       </c>
       <c r="F81">
-        <v>-2.140615830783017</v>
+        <v>-2.359643627389831</v>
       </c>
       <c r="G81">
-        <v>-4.387513501501988</v>
+        <v>-4.227878995598331</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.020585035528974</v>
       </c>
       <c r="E82">
-        <v>-18.79397074843894</v>
+        <v>-16.12525950318666</v>
       </c>
       <c r="F82">
-        <v>-2.071271538759865</v>
+        <v>-2.145223210277388</v>
       </c>
       <c r="G82">
-        <v>-4.241081451208945</v>
+        <v>-3.71068901872569</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.347730951246816</v>
       </c>
       <c r="E83">
-        <v>-18.70165780579258</v>
+        <v>-16.90309736958817</v>
       </c>
       <c r="F83">
-        <v>-2.547115596154401</v>
+        <v>-2.713636496567366</v>
       </c>
       <c r="G83">
-        <v>-3.373718519919894</v>
+        <v>-3.001272215115268</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.693812268932748</v>
       </c>
       <c r="E84">
-        <v>-17.31749802603008</v>
+        <v>-17.71000351064491</v>
       </c>
       <c r="F84">
-        <v>-2.556170480234403</v>
+        <v>-2.530019749695425</v>
       </c>
       <c r="G84">
-        <v>-3.497566028544029</v>
+        <v>-3.638803832885956</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.047362593609857</v>
       </c>
       <c r="E85">
-        <v>-20.18836035098477</v>
+        <v>-19.15810987186972</v>
       </c>
       <c r="F85">
-        <v>-2.170403922587687</v>
+        <v>-2.577505911060907</v>
       </c>
       <c r="G85">
-        <v>-3.698022871492439</v>
+        <v>-3.532065223608774</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.397345271046148</v>
       </c>
       <c r="E86">
-        <v>-20.09216197763983</v>
+        <v>-19.81887762822494</v>
       </c>
       <c r="F86">
-        <v>-2.397857872415778</v>
+        <v>-2.77381738838075</v>
       </c>
       <c r="G86">
-        <v>-4.540589816692348</v>
+        <v>-2.435394044996565</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.73035343799066</v>
       </c>
       <c r="E87">
-        <v>-21.64901058521083</v>
+        <v>-20.88133461448253</v>
       </c>
       <c r="F87">
-        <v>-2.509576470561736</v>
+        <v>-2.764891729615586</v>
       </c>
       <c r="G87">
-        <v>-3.239363339754112</v>
+        <v>-2.856505369228478</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.031981221520962</v>
       </c>
       <c r="E88">
-        <v>-23.33747476134076</v>
+        <v>-22.70506883769558</v>
       </c>
       <c r="F88">
-        <v>-2.453326182074635</v>
+        <v>-2.929729387466062</v>
       </c>
       <c r="G88">
-        <v>-3.181720120824322</v>
+        <v>-2.770242484111688</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.285704660521241</v>
       </c>
       <c r="E89">
-        <v>-26.31680762420117</v>
+        <v>-24.06295893973959</v>
       </c>
       <c r="F89">
-        <v>-2.399220536793383</v>
+        <v>-3.024681829379358</v>
       </c>
       <c r="G89">
-        <v>-3.667585715804379</v>
+        <v>-2.60212304999088</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.477750390671923</v>
       </c>
       <c r="E90">
-        <v>-25.30851118707531</v>
+        <v>-25.31202075443126</v>
       </c>
       <c r="F90">
-        <v>-2.95564071982563</v>
+        <v>-3.400375439408032</v>
       </c>
       <c r="G90">
-        <v>-5.476189712636857</v>
+        <v>-3.273481822081841</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.597522959902496</v>
       </c>
       <c r="E91">
-        <v>-28.41170687099352</v>
+        <v>-26.51115161471435</v>
       </c>
       <c r="F91">
-        <v>-3.038807978699298</v>
+        <v>-3.302277686466306</v>
       </c>
       <c r="G91">
-        <v>-3.473557952293234</v>
+        <v>-3.005102516304204</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.636375262462327</v>
       </c>
       <c r="E92">
-        <v>-29.38306001716481</v>
+        <v>-28.49494928020252</v>
       </c>
       <c r="F92">
-        <v>-3.088305416118777</v>
+        <v>-3.196775157310956</v>
       </c>
       <c r="G92">
-        <v>-4.572162489500378</v>
+        <v>-2.949217197055767</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.5890620261783</v>
       </c>
       <c r="E93">
-        <v>-31.40151862270769</v>
+        <v>-30.24888613353535</v>
       </c>
       <c r="F93">
-        <v>-2.491052518700334</v>
+        <v>-3.220527764218828</v>
       </c>
       <c r="G93">
-        <v>-4.108974131464328</v>
+        <v>-3.179710619681984</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.453043869085865</v>
       </c>
       <c r="E94">
-        <v>-33.22710272755288</v>
+        <v>-32.36932823796797</v>
       </c>
       <c r="F94">
-        <v>-3.345162266909237</v>
+        <v>-3.315179508764909</v>
       </c>
       <c r="G94">
-        <v>-3.91964072152787</v>
+        <v>-3.036026322186536</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.233012995816365</v>
       </c>
       <c r="E95">
-        <v>-35.98962357611104</v>
+        <v>-33.8132570819207</v>
       </c>
       <c r="F95">
-        <v>-2.458110832193205</v>
+        <v>-3.501605249499743</v>
       </c>
       <c r="G95">
-        <v>-4.31378103125134</v>
+        <v>-2.876272636643466</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.935506434971316</v>
       </c>
       <c r="E96">
-        <v>-38.25894605625684</v>
+        <v>-36.57452127894175</v>
       </c>
       <c r="F96">
-        <v>-3.124191120375454</v>
+        <v>-3.846859670945146</v>
       </c>
       <c r="G96">
-        <v>-4.103654084782719</v>
+        <v>-3.719005109120339</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.577083703690842</v>
       </c>
       <c r="E97">
-        <v>-39.31693796714287</v>
+        <v>-38.18503683197765</v>
       </c>
       <c r="F97">
-        <v>-3.004529307204052</v>
+        <v>-3.789111694193784</v>
       </c>
       <c r="G97">
-        <v>-4.710109611576269</v>
+        <v>-3.679152761918593</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.164185883166478</v>
       </c>
       <c r="E98">
-        <v>-40.83797993073522</v>
+        <v>-40.27316601012853</v>
       </c>
       <c r="F98">
-        <v>-2.4984398991985</v>
+        <v>-3.581595719383674</v>
       </c>
       <c r="G98">
-        <v>-4.668039198863211</v>
+        <v>-4.397915235586378</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.724669207455222</v>
       </c>
       <c r="E99">
-        <v>-43.09192371315097</v>
+        <v>-42.68387197726781</v>
       </c>
       <c r="F99">
-        <v>-4.067542545622754</v>
+        <v>-3.627821933929498</v>
       </c>
       <c r="G99">
-        <v>-5.25509823934217</v>
+        <v>-3.736335815018424</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.257895227635854</v>
       </c>
       <c r="E100">
-        <v>-45.33728150884816</v>
+        <v>-44.56977762013216</v>
       </c>
       <c r="F100">
-        <v>-3.19781227329926</v>
+        <v>-4.09724945742195</v>
       </c>
       <c r="G100">
-        <v>-5.174800957287148</v>
+        <v>-4.914853610998034</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.815549631615236</v>
       </c>
       <c r="E101">
-        <v>-47.79155592441523</v>
+        <v>-45.99887797594678</v>
       </c>
       <c r="F101">
-        <v>-3.685783629470782</v>
+        <v>-4.023386421216526</v>
       </c>
       <c r="G101">
-        <v>-5.821112141827983</v>
+        <v>-4.779664173356356</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.361087808860072</v>
       </c>
       <c r="E102">
-        <v>-49.80526076436856</v>
+        <v>-48.60409095866351</v>
       </c>
       <c r="F102">
-        <v>-3.644144913601662</v>
+        <v>-4.16829438772305</v>
       </c>
       <c r="G102">
-        <v>-5.551478139290962</v>
+        <v>-5.832831473037003</v>
       </c>
     </row>
   </sheetData>
